--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -8620,7 +8620,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46272.14767306713</v>
+        <v>46279.16746972222</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>366</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46223.59868443287</v>
+        <v>46279.167467129635</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>210</v>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46223.59868380787</v>
+        <v>46279.167468472224</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>246</v>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46223.59868314815</v>
+        <v>46279.16746438657</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>250</v>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46223.60164671297</v>
+        <v>46279.14919773148</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>384</v>
@@ -9103,8 +9103,8 @@
       <c r="S123" s="9">
         <v>0</v>
       </c>
-      <c r="T123" s="11" t="s">
-        <v>127</v>
+      <c r="T123" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="U123" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -8620,7 +8620,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46279.16746972222</v>
+        <v>46280.16525791667</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>366</v>
@@ -8667,8 +8667,8 @@
       <c r="S115" s="9">
         <v>0</v>
       </c>
-      <c r="T115" s="12" t="s">
-        <v>242</v>
+      <c r="T115" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>53</v>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46273.15093820602</v>
+        <v>46280.16749438657</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>376</v>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46223.598781168985</v>
+        <v>46280.167495891204</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>210</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46223.59878049769</v>
+        <v>46280.16749710648</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>246</v>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46223.598779803244</v>
+        <v>46280.167485625</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>250</v>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46118.542359756946</v>
+        <v>46280.1623034838</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>395</v>
@@ -9366,8 +9366,8 @@
       <c r="S128" s="6">
         <v>0</v>
       </c>
-      <c r="T128" s="11" t="s">
-        <v>127</v>
+      <c r="T128" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="U128" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6116,7 +6116,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46274.12746957176</v>
+        <v>46281.16740513888</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>238</v>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.54786737269</v>
+        <v>46281.16740662037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>210</v>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.54786818287</v>
+        <v>46281.16740770833</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>246</v>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.54786895833</v>
+        <v>46281.16740116898</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>249</v>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46280.16749438657</v>
+        <v>46281.16585435186</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>376</v>
@@ -8889,8 +8889,8 @@
       <c r="S119" s="9">
         <v>0</v>
       </c>
-      <c r="T119" s="12" t="s">
-        <v>242</v>
+      <c r="T119" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U119" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -739,433 +739,433 @@
     <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
   </si>
   <si>
+    <t>1213886259341627</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886259341647</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213881596172439</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213902113480432</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213902113480444</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213902113485641</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542206</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542236</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213902113596084</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213902113601428</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886181546547</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1213886304313737</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213902113612855</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Armado</t>
+  </si>
+  <si>
+    <t>1213881596172409</t>
+  </si>
+  <si>
+    <t>Armado,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886380584527</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886380584552</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886304333912</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886305136215</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213886259370468</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Tableros y componentes electricos ,Recepcion motor,Recepcion Rodete,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213902113620466</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,Bodega:</t>
+  </si>
+  <si>
+    <t>1213886380596164</t>
+  </si>
+  <si>
+    <t>OT 4299- TABLERO PLC,OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,Bodega:,OT 4298- TABLERO VDF ABB ACS880-17</t>
+  </si>
+  <si>
+    <t>1213886181569524</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886304340554</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Bodega:,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886380599685</t>
+  </si>
+  <si>
+    <t>Recepción Sensores</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213902113636476</t>
+  </si>
+  <si>
+    <t>Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,Bodega:</t>
+  </si>
+  <si>
+    <t>1213886259384757</t>
+  </si>
+  <si>
+    <t>Atenuadores</t>
+  </si>
+  <si>
+    <t>OT 4289  ATENUADORES 3,95X3,97X1,5M</t>
+  </si>
+  <si>
+    <t>1213886380568105</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,RE-PINTADO,Pruebas FAT,Montaje motor,Revestimiento,Montaje Sensores,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213886380568117</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886430692257</t>
+  </si>
+  <si>
+    <t>Recepcion Fabricacion externa,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886304363752</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Revestimiento</t>
+  </si>
+  <si>
+    <t>1213881596172413</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886430700837</t>
+  </si>
+  <si>
+    <t>Montaje Sensores</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886304369201</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepción Sensores,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Montaje Sensores,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886259405005</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepción Sensores,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>Montaje Sensores,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213881596172417</t>
+  </si>
+  <si>
+    <t>Montaje Sensores,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886181605565</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213886430706046</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepcion Alabe,Recepcion Fabricacion externa,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213886380630758</t>
+  </si>
+  <si>
+    <t>Check Planos,OT 4296 ZVR1-14-34/4,Recepcion Fabricacion externa,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213881596172420</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886430709523</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213886380639335</t>
+  </si>
+  <si>
+    <t>Recepcion Fabricacion externa,OT 4294 ZVR 1-14-42/4,Check Planos,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213886181616620</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Recepcion Rodete,Check Planos,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213881596172424</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886430714243</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1213886259427564</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepcion motor,OT 4294 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213886380645167</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepcion motor,OT 4296 ZVR1-14-34/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213881596172430</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886259403689</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213886304408781</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886304408811</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213881596172434</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886181642573</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213886259341627</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886259341647</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213881596172439</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213902113480432</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213902113480444</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213902113485641</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542206</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542236</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213902113596084</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213902113601428</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886181546547</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1213886304313737</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213902113612855</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Armado</t>
-  </si>
-  <si>
-    <t>1213881596172409</t>
-  </si>
-  <si>
-    <t>Armado,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886380584527</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886380584552</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886304333912</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886305136215</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213886259370468</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Tableros y componentes electricos ,Recepcion motor,Recepcion Rodete,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213902113620466</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,Bodega:</t>
-  </si>
-  <si>
-    <t>1213886380596164</t>
-  </si>
-  <si>
-    <t>OT 4299- TABLERO PLC,OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,Bodega:,OT 4298- TABLERO VDF ABB ACS880-17</t>
-  </si>
-  <si>
-    <t>1213886181569524</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886304340554</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Bodega:,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886380599685</t>
-  </si>
-  <si>
-    <t>Recepción Sensores</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213902113636476</t>
-  </si>
-  <si>
-    <t>Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,Bodega:</t>
-  </si>
-  <si>
-    <t>1213886259384757</t>
-  </si>
-  <si>
-    <t>Atenuadores</t>
-  </si>
-  <si>
-    <t>OT 4289  ATENUADORES 3,95X3,97X1,5M</t>
-  </si>
-  <si>
-    <t>1213886380568105</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,RE-PINTADO,Pruebas FAT,Montaje motor,Revestimiento,Montaje Sensores,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213886380568117</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886430692257</t>
-  </si>
-  <si>
-    <t>Recepcion Fabricacion externa,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886304363752</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213881596172413</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886430700837</t>
-  </si>
-  <si>
-    <t>Montaje Sensores</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886304369201</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepción Sensores,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Montaje Sensores,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886259405005</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepción Sensores,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>Montaje Sensores,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213881596172417</t>
-  </si>
-  <si>
-    <t>Montaje Sensores,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886181605565</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213886430706046</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepcion Alabe,Recepcion Fabricacion externa,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213886380630758</t>
-  </si>
-  <si>
-    <t>Check Planos,OT 4296 ZVR1-14-34/4,Recepcion Fabricacion externa,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213881596172420</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886430709523</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213886380639335</t>
-  </si>
-  <si>
-    <t>Recepcion Fabricacion externa,OT 4294 ZVR 1-14-42/4,Check Planos,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213886181616620</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Recepcion Rodete,Check Planos,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213881596172424</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886430714243</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1213886259427564</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepcion motor,OT 4294 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213886380645167</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepcion motor,OT 4296 ZVR1-14-34/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213881596172430</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886259403689</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213886304408781</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886304408811</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213881596172434</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886181642573</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
   </si>
   <si>
     <t>1213886181643829</t>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46281.16740513888</v>
+        <v>46282.14671855324</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>238</v>
@@ -6163,8 +6163,8 @@
       <c r="S71" s="9">
         <v>0</v>
       </c>
-      <c r="T71" s="12" t="s">
-        <v>242</v>
+      <c r="T71" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>53</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6215,7 +6215,7 @@
         <v>210</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6235,7 +6235,7 @@
         <v>46281.16740770833</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -6265,10 +6265,10 @@
         <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6288,7 +6288,7 @@
         <v>46281.16740116898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6318,10 +6318,10 @@
         <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6343,7 +6343,7 @@
         <v>46260.658590023144</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6367,7 +6367,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6396,16 +6396,16 @@
         <v>46260.65857824074</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6421,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6459,7 +6459,7 @@
         <v>46237.86033361111</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6483,7 +6483,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6512,16 +6512,16 @@
         <v>46237.86031981482</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6539,13 +6539,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6577,16 +6577,16 @@
         <v>46237.86032310185</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6604,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6625,12 +6625,12 @@
         <v>31</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6640,7 +6640,7 @@
         <v>46265.8665325926</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6664,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6677,7 +6677,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6689,16 +6689,16 @@
         <v>46260.58243447916</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6716,13 +6716,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6752,16 +6752,16 @@
         <v>46260.65928364583</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6779,13 +6779,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>241</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6823,10 +6823,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6844,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6872,16 +6872,16 @@
         <v>46260.58353350694</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6899,13 +6899,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6915,7 +6915,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6925,16 +6925,16 @@
         <v>46260.58241299768</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6952,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6980,16 +6980,16 @@
         <v>46265.866544212964</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -7007,13 +7007,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7033,7 +7033,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7049,10 +7049,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7070,13 +7070,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O87" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7086,7 +7086,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7096,16 +7096,16 @@
         <v>46260.583538541665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7123,13 +7123,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7149,16 +7149,16 @@
         <v>46247.16738921296</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7176,13 +7176,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7202,7 +7202,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7226,7 +7226,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7249,16 +7249,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7276,13 +7276,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7318,10 +7318,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7339,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7365,7 +7365,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7375,16 +7375,16 @@
         <v>46248.18939703704</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7402,13 +7402,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7423,12 +7423,12 @@
         <v>31</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7438,16 +7438,16 @@
         <v>46275.16202614583</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7465,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7501,16 +7501,16 @@
         <v>46224.16695678241</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7528,13 +7528,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>178</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7549,12 +7549,12 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7564,16 +7564,16 @@
         <v>46260.6585802662</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7589,13 +7589,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7610,12 +7610,12 @@
         <v>31</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7625,16 +7625,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7652,13 +7652,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>198</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7673,12 +7673,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7688,7 +7688,7 @@
         <v>46221.897785625</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7712,7 +7712,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7725,7 +7725,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7735,7 +7735,7 @@
         <v>46268.182027939816</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7762,13 +7762,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7788,7 +7788,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7825,13 +7825,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>329</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7851,7 +7851,7 @@
         <v>46267.16748722222</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7878,13 +7878,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7904,7 +7904,7 @@
         <v>46267.16750917824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7931,13 +7931,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7947,7 +7947,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7957,7 +7957,7 @@
         <v>46270.17116346065</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7984,13 +7984,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -8010,7 +8010,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -8047,13 +8047,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8063,7 +8063,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8073,7 +8073,7 @@
         <v>46269.167709421294</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8100,13 +8100,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O105" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="P105" s="9" t="s">
         <v>343</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>344</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8126,7 +8126,7 @@
         <v>46269.1677040625</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8153,13 +8153,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8179,7 +8179,7 @@
         <v>46274.15587163194</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8206,13 +8206,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8232,7 +8232,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8269,13 +8269,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>350</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8285,7 +8285,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8295,7 +8295,7 @@
         <v>46273.1674940625</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8322,13 +8322,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O109" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="P109" s="9" t="s">
         <v>353</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>354</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8338,7 +8338,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8348,7 +8348,7 @@
         <v>46273.16747483796</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8375,13 +8375,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8391,7 +8391,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8401,7 +8401,7 @@
         <v>46276.1559318287</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8428,13 +8428,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>241</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8454,7 +8454,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8491,13 +8491,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8507,7 +8507,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8517,7 +8517,7 @@
         <v>46275.16748549769</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8544,13 +8544,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8560,7 +8560,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8570,7 +8570,7 @@
         <v>46275.167477662035</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8597,13 +8597,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8613,7 +8613,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8623,7 +8623,7 @@
         <v>46280.16525791667</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8650,13 +8650,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8713,13 +8713,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8739,7 +8739,7 @@
         <v>46279.167468472224</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8766,13 +8766,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="P117" s="9" t="s">
         <v>371</v>
-      </c>
-      <c r="P117" s="9" t="s">
-        <v>372</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8782,7 +8782,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8792,7 +8792,7 @@
         <v>46279.16746438657</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8819,13 +8819,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8835,7 +8835,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8845,7 +8845,7 @@
         <v>46281.16585435186</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8872,13 +8872,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8898,7 +8898,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8933,13 +8933,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8949,7 +8949,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8959,7 +8959,7 @@
         <v>46280.16749710648</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8984,13 +8984,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9000,7 +9000,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -9010,7 +9010,7 @@
         <v>46280.167485625</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9035,13 +9035,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9051,7 +9051,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9061,7 +9061,7 @@
         <v>46279.14919773148</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9086,13 +9086,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="T123" s="12" t="s">
-        <v>242</v>
+        <v>384</v>
       </c>
       <c r="U123" s="10" t="s">
         <v>53</v>
@@ -9147,7 +9147,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>210</v>
@@ -9173,7 +9173,7 @@
         <v>46223.59886280092</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9198,10 +9198,10 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>388</v>
@@ -9224,7 +9224,7 @@
         <v>46223.59886211806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9249,10 +9249,10 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>390</v>
@@ -9367,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="T128" s="12" t="s">
-        <v>242</v>
+        <v>384</v>
       </c>
       <c r="U128" s="10" t="s">
         <v>53</v>
@@ -9436,7 +9436,7 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9464,7 +9464,7 @@
         <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>402</v>
@@ -9487,7 +9487,7 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9515,7 +9515,7 @@
         <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>404</v>
@@ -9742,7 +9742,7 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9770,7 +9770,7 @@
         <v>395</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>414</v>
@@ -9909,7 +9909,7 @@
         <v>46223.601775636576</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9939,7 +9939,7 @@
         <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>422</v>
@@ -9962,7 +9962,7 @@
         <v>46223.601775</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9992,7 +9992,7 @@
         <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>424</v>
@@ -10257,7 +10257,7 @@
         <v>416</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>435</v>
@@ -10286,10 +10286,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10347,10 +10347,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10394,16 +10394,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10424,7 +10424,7 @@
         <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>442</v>
@@ -10447,16 +10447,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10477,10 +10477,10 @@
         <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10506,10 +10506,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10559,10 +10559,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10612,10 +10612,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10665,10 +10665,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10718,10 +10718,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10771,10 +10771,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10834,10 +10834,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10881,16 +10881,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10911,7 +10911,7 @@
         <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>456</v>
@@ -10940,10 +10940,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10987,16 +10987,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11017,7 +11017,7 @@
         <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11046,10 +11046,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11099,10 +11099,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11152,10 +11152,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11205,10 +11205,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -9790,7 +9790,7 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46223.601863715274</v>
+        <v>46283.12825015046</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>416</v>
@@ -9837,8 +9837,8 @@
       <c r="S137" s="9">
         <v>0</v>
       </c>
-      <c r="T137" s="11" t="s">
-        <v>127</v>
+      <c r="T137" s="12" t="s">
+        <v>384</v>
       </c>
       <c r="U137" s="10" t="s">
         <v>53</v>
